--- a/docs/build/lakeshore-enterprise-context/source/12_ai_use_cases_moves/cost_optimization_use_case.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/12_ai_use_cases_moves/cost_optimization_use_case.xlsx
@@ -485,15 +485,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FX hedge advisor</t>
+          <t>Knowledge deflection bot</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12m</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -510,11 +510,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler</t>
+          <t>Audit evidence assembler</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -560,11 +560,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spend optimization agent</t>
+          <t>Payment anomaly detection</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Payment anomaly detection</t>
+          <t>Liquidity scenario modeler</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12m</t>
+          <t>18m</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -610,20 +610,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audit evidence assembler</t>
+          <t>Working capital optimizer</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -635,15 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler</t>
+          <t>Vendor scorecard agent</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -660,15 +660,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent</t>
+          <t>Spend optimization agent</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6m</t>
+          <t>18m</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -685,15 +685,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Contract risk extractor</t>
+          <t>Bank fee analyzer</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -710,11 +710,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SoD conflict detector</t>
+          <t>Payment anomaly detection</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -760,15 +760,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Knowledge deflection bot</t>
+          <t>Spend optimization agent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -785,15 +785,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent</t>
+          <t>Audit evidence assembler</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -810,11 +810,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Working capital optimizer</t>
+          <t>Cash forecasting copilot</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
